--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/6931-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/6931-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4594FAE6-1637-47D3-B48F-D009AF8BDDBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{470C8E91-8BCE-4A51-9CD4-5C532DCB3211}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{E9FAEFB5-DED4-496F-938B-770E748C9C42}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{E254B57A-06C2-42C7-85C3-F8AE8B30E9B8}"/>
   </bookViews>
   <sheets>
     <sheet name="6931-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1475,23 +1475,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2461DD9-E708-4941-A173-4D945680649B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FA9A1D6-6DF2-4FEC-AC31-B0B3F84F8CDB}">
   <dimension ref="A1:R20"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="6" width="8" customWidth="1"/>
-    <col min="7" max="7" width="8.33203125" customWidth="1"/>
-    <col min="8" max="8" width="8" customWidth="1"/>
-    <col min="9" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.6640625" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="3" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="10.5" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="10.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1519,7 +1519,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1549,7 +1549,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1595,7 +1595,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1645,7 +1645,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2025</v>
       </c>
@@ -1699,7 +1699,7 @@
         <v>1.37</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
@@ -1755,7 +1755,7 @@
         <v>0.19</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>25</v>
       </c>
@@ -1811,7 +1811,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>25</v>
       </c>
@@ -1867,7 +1867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>25</v>
       </c>
@@ -1923,7 +1923,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="39">
         <v>2024</v>
       </c>
@@ -1977,7 +1977,7 @@
         <v>0.96</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
         <v>25</v>
       </c>
@@ -2033,7 +2033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
         <v>25</v>
       </c>
@@ -2089,7 +2089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="17" t="s">
         <v>25</v>
       </c>
@@ -2145,7 +2145,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
         <v>25</v>
       </c>
@@ -2201,7 +2201,7 @@
         <v>0.96</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="37">
         <v>2023</v>
       </c>
@@ -2255,7 +2255,7 @@
         <v>0.69</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>25</v>
       </c>
@@ -2311,7 +2311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>25</v>
       </c>
@@ -2367,7 +2367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>25</v>
       </c>
@@ -2423,7 +2423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>25</v>
       </c>
@@ -2479,7 +2479,7 @@
         <v>0.69</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="39" t="s">
         <v>44</v>
       </c>
